--- a/bms_sa_review/synthetic_ami_creation/notebooks/ami_dataset_column_reference.xlsx
+++ b/bms_sa_review/synthetic_ami_creation/notebooks/ami_dataset_column_reference.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unsw-my.sharepoint.com/personal/z3553082_ad_unsw_edu_au/Documents/Documents/GitHub/CICCADA/bms_sa_review/ami_data_analysis/notebooks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unsw-my.sharepoint.com/personal/z3553082_ad_unsw_edu_au/Documents/Documents/GitHub/CICCADA/bms_sa_review/synthetic_ami_creation/notebooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="53" documentId="11_FD25D7C65C90A3E4CC61D21805B5FB9F898F4A10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCFE49BB-DF0F-4048-A7DD-40C4C754AA9E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ami_meter" sheetId="2" r:id="rId1"/>
